--- a/outputs/programacion_visual.xlsx
+++ b/outputs/programacion_visual.xlsx
@@ -38,7 +38,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -62,17 +62,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8E8E8"/>
+        <fgColor rgb="00B8E0B0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A8D8EA"/>
+        <fgColor rgb="00FFA420"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00e6eff9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009BC4D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008fedf2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00CCA9DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002686ab"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -120,6 +140,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -491,24 +523,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -520,109 +552,109 @@
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>S1
-27-Jul</t>
+27-Jul - 01-Aug</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>S2
-03-Aug</t>
+03-Aug - 08-Aug</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>S3
-10-Aug</t>
+10-Aug - 15-Aug</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>S4
-17-Aug</t>
+17-Aug - 22-Aug</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>S5
-24-Aug</t>
+24-Aug - 29-Aug</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>S6
-31-Aug</t>
+31-Aug - 05-Sep</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>S7
-07-Sep</t>
+07-Sep - 12-Sep</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>S9
-21-Sep</t>
+21-Sep - 26-Sep</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>S10
-28-Sep</t>
+28-Sep - 03-Oct</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>S11
-05-Oct</t>
+05-Oct - 10-Oct</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>S12
-12-Oct</t>
+12-Oct - 17-Oct</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>S13
-19-Oct</t>
+19-Oct - 24-Oct</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>S14
-26-Oct</t>
+26-Oct - 31-Oct</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>S15
-02-Nov</t>
+02-Nov - 07-Nov</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>S16
-09-Nov</t>
+09-Nov - 14-Nov</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>S17
-16-Nov</t>
+16-Nov - 21-Nov</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>S18
-23-Nov</t>
+23-Nov - 28-Nov</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>S19
-30-Nov</t>
+30-Nov - 05-Dec</t>
         </is>
       </c>
     </row>
@@ -636,67 +668,67 @@
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (05-Aug)</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (12-Aug)</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (19-Aug)</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (26-Aug)</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (02-Sep)</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (09-Sep)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (23-Sep)</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (30-Sep)</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (07-Oct)</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (14-Oct)</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (21-Oct)</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (28-Oct)</t>
         </is>
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>CIG029</t>
+          <t>400CIG029 (04-Nov)</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
@@ -711,118 +743,102 @@
 14:00 – 17:00</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>CIG028
-CIS021
-FTA005</t>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>400CIG028 (31-Jul)
+400FTA005 (31-Jul)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>CIG028
-CIS021
-FTA005</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>CIG028
-CIS021
-FTA005</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CIG028
-CIS021
-FTA005</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>CID002
-CIG028
-FTA005</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>CIG028
-CIS021
-FTA005</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>CIG028
-CIS021
-FTA005</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>CIG028
-CIS021
-FTA005</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>CIG028
-CIS021
-FTA005</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>CID002
-CIG028
-FTA005</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>CIG028
-CIS021
-FTA005</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>CIG028
-CIS021
-FTA005</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>CID002
-FTA005</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>CID002
-FTA005</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>CID002
-FTA005</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>CID002
-FTA005</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>CID002</t>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>400CIG028 (14-Aug)
+400FTA005 (14-Aug)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>400CIG028 (21-Aug)
+400FTA005 (21-Aug)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>400CIG028 (28-Aug)
+400FTA005 (28-Aug)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>400CIG028 (04-Sep)
+400FTA005 (04-Sep)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>400CIG028 (11-Sep)
+400FTA005 (11-Sep)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>400CIG028 (25-Sep)
+400FTA005 (25-Sep)</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>400CIG028 (02-Oct)
+400FTA005 (02-Oct)</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>400CIG028 (09-Oct)
+400FTA005 (09-Oct)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>400CIG028 (16-Oct)
+400FTA005 (16-Oct)</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>400CIG028 (23-Oct)
+400FTA005 (23-Oct)</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>400CIG028 (30-Oct)
+400FTA005 (30-Oct)</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>400FTA005 (06-Nov)</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>400FTA005 (13-Nov)</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>400FTA005 (20-Nov)</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>400FTA005 (27-Nov)</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (04-Dec)</t>
         </is>
       </c>
     </row>
@@ -833,31 +849,87 @@
 17:00 – 19:00</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (31-Jul)</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>CIS021</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>CIS021</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (14-Aug)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (21-Aug)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (28-Aug)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (04-Sep)</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (11-Sep)</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (25-Sep)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (02-Oct)</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (09-Oct)</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (16-Oct)</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (23-Oct)</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (30-Oct)</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (06-Nov)</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (13-Nov)</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (20-Nov)</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (27-Nov)</t>
+        </is>
+      </c>
       <c r="S4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -867,82 +939,90 @@
 19:00 – 21:00</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (31-Jul)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (14-Aug)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (21-Aug)</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (28-Aug)</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (04-Sep)</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (11-Sep)</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (25-Sep)</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (02-Oct)</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (09-Oct)</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (16-Oct)</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (23-Oct)</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (30-Oct)</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (06-Nov)</t>
+        </is>
+      </c>
+      <c r="P5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (13-Nov)</t>
+        </is>
+      </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (20-Nov)</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (27-Nov)</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (04-Dec)</t>
         </is>
       </c>
     </row>
@@ -953,132 +1033,96 @@
 07:00 – 10:00</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>CIS002
-CIS021</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>CIG037
-CIS002
-ITA003
-ITA005</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>CIG037
-CIS002
-ITA003
-ITA005</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>CIG037
-CIS002
-ITA003
-ITA005</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>CIG037
-ITA003
-ITA005</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>CIG037
-CIS021
-ITA003
-ITA005</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>CID002
-CIG037
-ITA003
-ITA005</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>CID002
-CIG037
-ITA003
-ITA005</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>CID002
-CIG037
-ITA003
-ITA005</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>CID002
-CIG037
-ITA003
-ITA005</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>CID002
-CIS021</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>CID002
-CIG037
-ITA003
-ITA005</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>CID002
-CIG037
-ITA003
-ITA005</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>CID002
-CIS021</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>CID002
-CIS021</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>CIS021</t>
-        </is>
-      </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>CID002
-CIS021</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr">
-        <is>
-          <t>CID002
-CIS002</t>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (01-Aug)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (08-Aug)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (15-Aug)</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (22-Aug)</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>400CIG037 (29-Aug)
+400ITA003 (29-Aug)
+400ITA005 (29-Aug)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (05-Sep)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (12-Sep)</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (26-Sep)</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (03-Oct)</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (10-Oct)</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (17-Oct)</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (24-Oct)</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (31-Oct)</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (07-Nov)</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (14-Nov)</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (21-Nov)</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (28-Nov)</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (05-Dec)</t>
         </is>
       </c>
     </row>
@@ -1089,36 +1133,116 @@
 10:00 – 13:00</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>CIG037
-ITA003
-ITA005</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>CIS021</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr">
-        <is>
-          <t>CIS002</t>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (01-Aug)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>400CIG037 (08-Aug)
+400ITA003 (08-Aug)
+400ITA005 (08-Aug)</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>400CIG037 (15-Aug)
+400ITA003 (15-Aug)
+400ITA005 (15-Aug)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>400CIG037 (22-Aug)
+400ITA003 (22-Aug)
+400ITA005 (22-Aug)</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>400CIG037 (29-Aug)
+400ITA003 (29-Aug)
+400ITA005 (29-Aug)</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>400CIG037 (05-Sep)
+400ITA003 (05-Sep)
+400ITA005 (05-Sep)</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>400CIG037 (12-Sep)
+400ITA003 (12-Sep)
+400ITA005 (12-Sep)</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>400CIG037 (26-Sep)
+400ITA003 (26-Sep)
+400ITA005 (26-Sep)</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>400CIG037 (03-Oct)
+400ITA003 (03-Oct)
+400ITA005 (03-Oct)</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>400CIG037 (10-Oct)
+400ITA003 (10-Oct)
+400ITA005 (10-Oct)</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (17-Oct)</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>400CIG037 (24-Oct)
+400ITA003 (24-Oct)
+400ITA005 (24-Oct)</t>
+        </is>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>400CIG037 (31-Oct)
+400ITA003 (31-Oct)
+400ITA005 (31-Oct)</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (07-Nov)</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (14-Nov)</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>400CIS021 (21-Nov)</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>400CID002 (28-Nov)</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>400CIS002 (05-Dec)</t>
         </is>
       </c>
     </row>
@@ -1130,64 +1254,64 @@
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (08-Aug)</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (15-Aug)</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (22-Aug)</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (29-Aug)</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (05-Sep)</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (12-Sep)</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (26-Sep)</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (03-Oct)</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (10-Oct)</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (17-Oct)</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (24-Oct)</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (31-Oct)</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr"/>
@@ -1204,64 +1328,64 @@
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>ITA007</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (08-Aug)</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (15-Aug)</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (22-Aug)</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (29-Aug)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (05-Sep)</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (12-Sep)</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (26-Sep)</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (03-Oct)</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (10-Oct)</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (17-Oct)</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (24-Oct)</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (31-Oct)</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr"/>

--- a/outputs/programacion_visual.xlsx
+++ b/outputs/programacion_visual.xlsx
@@ -681,11 +681,7 @@
           <t>400CIG029 (19-Aug)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>400CIG029 (26-Aug)</t>
-        </is>
-      </c>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="4" t="inlineStr">
         <is>
           <t>400CIG029 (02-Sep)</t>
@@ -711,11 +707,7 @@
           <t>400CIG029 (07-Oct)</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>400CIG029 (14-Oct)</t>
-        </is>
-      </c>
+      <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="4" t="inlineStr">
         <is>
           <t>400CIG029 (21-Oct)</t>
@@ -726,15 +718,27 @@
           <t>400CIG029 (28-Oct)</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>400CIG029 (04-Nov)</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>400CIG029 (11-Nov)</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>400CIG029 (18-Nov)</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>400CIG029 (25-Nov)</t>
+        </is>
+      </c>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>400CIG029 (02-Dec)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1254,11 +1258,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>400ITA007 (08-Aug)</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="10" t="inlineStr">
         <is>
           <t>400ITA007 (15-Aug)</t>
@@ -1314,7 +1314,11 @@
           <t>400ITA007 (31-Oct)</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr"/>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (07-Nov)</t>
+        </is>
+      </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="3" t="inlineStr"/>
@@ -1328,11 +1332,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>400ITA007 (08-Aug)</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="10" t="inlineStr">
         <is>
           <t>400ITA007 (15-Aug)</t>
@@ -1388,7 +1388,11 @@
           <t>400ITA007 (31-Oct)</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr"/>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>400ITA007 (07-Nov)</t>
+        </is>
+      </c>
       <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr"/>
       <c r="R9" s="3" t="inlineStr"/>
